--- a/Översikt ANEBY.xlsx
+++ b/Översikt ANEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45293</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45109</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44886</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>45202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44565</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>45393</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45792</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45996</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>45912</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>45539</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>45293</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>45709</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>46072</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>45365</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46283</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>46283</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45205</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>46184</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44677</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44508</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>44747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>45467</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45707</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>45461</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45365</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
         <v>44985</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>45936</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44740</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>44565</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45547</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>45386</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45161</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>45229</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
         <v>46174</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>46176</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>44460</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>46268</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45558</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5610,7 +5610,7 @@
         <v>44533</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>44461</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         <v>44739</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>44888</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>44747</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>44743</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         <v>44539</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6272,7 +6272,7 @@
         <v>44853</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6345,7 +6345,7 @@
         <v>44585</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6418,7 +6418,7 @@
         <v>44853</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         <v>44624</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>44826</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6637,7 +6637,7 @@
         <v>44621</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>44624</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>44739</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6929,7 +6929,7 @@
         <v>44739</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7002,7 +7002,7 @@
         <v>44606</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7075,7 +7075,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         <v>44826</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>44888</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         <v>44886</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>44565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>44606</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7513,7 +7513,7 @@
         <v>44503</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7586,7 +7586,7 @@
         <v>44959</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>45419</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>45775</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>45359</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>45617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         <v>45468</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8034,7 +8034,7 @@
         <v>45107</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>45126</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45182</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45769</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>45033</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44985</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>45769</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         <v>44888</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8618,7 +8618,7 @@
         <v>45122</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>44847</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45365</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         <v>45028</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>44888</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         <v>45007</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9061,7 +9061,7 @@
         <v>45384</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9212,7 +9212,7 @@
         <v>44852</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>45665</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9363,7 +9363,7 @@
         <v>45363</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>45762</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         <v>45300</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>45727</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9660,7 +9660,7 @@
         <v>45653</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>45461</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>45250</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9879,7 +9879,7 @@
         <v>45141</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9952,7 +9952,7 @@
         <v>45236</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10025,7 +10025,7 @@
         <v>45300</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10098,7 +10098,7 @@
         <v>44678</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
         <v>45183</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10244,7 +10244,7 @@
         <v>45304</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10317,7 +10317,7 @@
         <v>45475</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10390,7 +10390,7 @@
         <v>44860</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10463,7 +10463,7 @@
         <v>45146</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10536,7 +10536,7 @@
         <v>45553</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>44482</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>45586</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10760,7 +10760,7 @@
         <v>45020</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45330</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>45358</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45357</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45086</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>45148</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11203,7 +11203,7 @@
         <v>44481</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>44482</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11349,7 +11349,7 @@
         <v>45359</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>45124</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>45749</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>45691</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>45205</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45159</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>45608</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45889</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>45889</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>45840</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12084,7 +12084,7 @@
         <v>45552</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         <v>45924</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>44705</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>45356</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45552</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>45189</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>45572</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>44477</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>45903</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>45839</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>45908</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45909</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12960,7 +12960,7 @@
         <v>45909</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45771</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>45911</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>45912</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>44606</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>45924</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45393</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>45000</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>44985</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>45454</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44705</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13768,7 +13768,7 @@
         <v>45936</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13841,7 +13841,7 @@
         <v>46147</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13914,7 +13914,7 @@
         <v>45537</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>45097</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14060,7 +14060,7 @@
         <v>45946</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45665</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14211,7 +14211,7 @@
         <v>45379</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14284,7 +14284,7 @@
         <v>45951</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>45146</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14430,7 +14430,7 @@
         <v>45953</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>44739</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>45412</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14649,7 +14649,7 @@
         <v>45357</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14722,7 +14722,7 @@
         <v>45960</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>45645</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14868,7 +14868,7 @@
         <v>45951</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45967</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15014,7 +15014,7 @@
         <v>45967</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15087,7 +15087,7 @@
         <v>45372</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15160,7 +15160,7 @@
         <v>45357</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>44952</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15306,7 +15306,7 @@
         <v>45707</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15379,7 +15379,7 @@
         <v>44550</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>44623</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45076</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15598,7 +15598,7 @@
         <v>45393</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45978</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>45467</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15842,7 +15842,7 @@
         <v>45980</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15915,7 +15915,7 @@
         <v>45068</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15988,7 +15988,7 @@
         <v>45980</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45980</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>45982</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16207,7 +16207,7 @@
         <v>45033</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>45077</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16353,7 +16353,7 @@
         <v>45077</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>45993</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         <v>45159</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>45978</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>45610</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16718,7 +16718,7 @@
         <v>45198</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>44721</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45616</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
         <v>46000</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>46000</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17088,7 +17088,7 @@
         <v>46000</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>46006</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>45772</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>46006</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>45316</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44966</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>45184</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>44999</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>45084</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>45198</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17823,7 +17823,7 @@
         <v>45665</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>46020</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>46021</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18047,7 +18047,7 @@
         <v>46170</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>46021</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44957</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>46030</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45275</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>46035</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>46171</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>45343</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>45304</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>46045</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44578</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>45468</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>46051</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>46176</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>46176</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45439</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45593</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19293,7 +19293,7 @@
         <v>46056</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19366,7 +19366,7 @@
         <v>46057</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>46057</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>46030</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19585,7 +19585,7 @@
         <v>46057</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19658,7 +19658,7 @@
         <v>44890</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19731,7 +19731,7 @@
         <v>44890</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
         <v>46058</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19877,7 +19877,7 @@
         <v>46059</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>46058</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20023,7 +20023,7 @@
         <v>45364</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20096,7 +20096,7 @@
         <v>46064</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20169,7 +20169,7 @@
         <v>45393</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20242,7 +20242,7 @@
         <v>44859</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20320,7 +20320,7 @@
         <v>45763</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>44851</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20471,7 +20471,7 @@
         <v>46073</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20544,7 +20544,7 @@
         <v>45372</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20617,7 +20617,7 @@
         <v>46076</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20690,7 +20690,7 @@
         <v>44620</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20763,7 +20763,7 @@
         <v>46084</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20836,7 +20836,7 @@
         <v>46185</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20914,7 +20914,7 @@
         <v>46185</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20992,7 +20992,7 @@
         <v>44981</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>46185</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>45379</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>46184</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>46090</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>45126</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>46184</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>44461</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>46184</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21669,7 +21669,7 @@
         <v>44671</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>46093</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21820,7 +21820,7 @@
         <v>46098</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>46195</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45356</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45539</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>46195</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22200,7 +22200,7 @@
         <v>46104</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>46104</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22346,7 +22346,7 @@
         <v>46196</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45365</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45365</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>46105</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>46105</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>46105</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45110</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22872,7 +22872,7 @@
         <v>45365</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>46125</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23023,7 +23023,7 @@
         <v>44959</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23096,7 +23096,7 @@
         <v>46125</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23169,7 +23169,7 @@
         <v>45034</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>45574</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>46126</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>44524</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45033</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>44900</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23617,7 +23617,7 @@
         <v>45076</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45460</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>45156</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23836,7 +23836,7 @@
         <v>45363</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23909,7 +23909,7 @@
         <v>45077</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23982,7 +23982,7 @@
         <v>45092</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24055,7 +24055,7 @@
         <v>45161</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24133,7 +24133,7 @@
         <v>45028</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24206,7 +24206,7 @@
         <v>45616</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24279,7 +24279,7 @@
         <v>45408</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45016</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24425,7 +24425,7 @@
         <v>44978</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>45009</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>45372</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24644,7 +24644,7 @@
         <v>45378</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24717,7 +24717,7 @@
         <v>44994</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45555</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24863,7 +24863,7 @@
         <v>45184</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24936,7 +24936,7 @@
         <v>46254</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25009,7 +25009,7 @@
         <v>44957</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25082,7 +25082,7 @@
         <v>44700</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45159</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>45357</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25301,7 +25301,7 @@
         <v>45357</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25374,7 +25374,7 @@
         <v>46254</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>44461</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25520,7 +25520,7 @@
         <v>45089</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25593,7 +25593,7 @@
         <v>46214</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25666,7 +25666,7 @@
         <v>46214</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25739,7 +25739,7 @@
         <v>46214</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>46255</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>45586</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25968,7 +25968,7 @@
         <v>45404</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26041,7 +26041,7 @@
         <v>44461</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26114,7 +26114,7 @@
         <v>45365</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26192,7 +26192,7 @@
         <v>46265</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26265,7 +26265,7 @@
         <v>46265</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26338,7 +26338,7 @@
         <v>46265</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>46267</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>46224</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45600</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45161</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26703,7 +26703,7 @@
         <v>44565</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45775</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>46273</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26927,7 +26927,7 @@
         <v>45001</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>46273</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>45698</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27146,7 +27146,7 @@
         <v>45594</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45201</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45398</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>46283</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45796</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27511,7 +27511,7 @@
         <v>45531</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45812</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27657,7 +27657,7 @@
         <v>45819</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27730,7 +27730,7 @@
         <v>45824</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27808,7 +27808,7 @@
         <v>45831</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>45838</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>45688</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>44848</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>44886</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>45063</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28251,7 +28251,7 @@
         <v>44475</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28324,7 +28324,7 @@
         <v>45546</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28397,7 +28397,7 @@
         <v>44886</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28470,7 +28470,7 @@
         <v>45069</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>45135</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28616,7 +28616,7 @@
         <v>44603</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28689,7 +28689,7 @@
         <v>44886</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28762,7 +28762,7 @@
         <v>44886</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>45702</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28908,7 +28908,7 @@
         <v>46029</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         <v>46135</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>

--- a/Översikt ANEBY.xlsx
+++ b/Översikt ANEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45293</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45109</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44886</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>45202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44565</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>45393</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45792</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>46126</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>45996</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45539</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45912</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>46072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>45293</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>46283</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>45365</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45709</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>46283</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45205</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>46184</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44677</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44508</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45461</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>45547</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>45558</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>45386</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45936</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44747</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45161</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44565</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46176</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>46174</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>45365</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>46268</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>44985</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45707</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45467</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>44533</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>44532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>44739</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>44888</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>44747</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>44743</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44539</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44853</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44585</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44853</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>44624</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44621</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44826</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>44739</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44739</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44606</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44888</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44886</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44565</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>44503</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45033</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45771</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>45189</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>45749</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45107</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45205</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45092</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>45419</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45460</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45250</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45393</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45393</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45461</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44860</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>44957</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>46020</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>44852</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>46021</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>46021</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45796</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45454</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>46030</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45356</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45330</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45205</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45840</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>46035</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44890</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>44890</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45889</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45275</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45467</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45889</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45156</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>44550</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45475</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>46045</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45665</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>45908</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>46051</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45909</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>44859</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>45909</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45439</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44999</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>46056</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45912</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>46057</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>46058</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>46058</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>46057</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>46057</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>46030</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>45911</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>46059</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>46064</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45555</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>45531</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>45924</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>46076</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>46073</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>45358</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>46084</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45936</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>46090</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44888</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>46093</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45586</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>46098</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45539</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45946</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>46104</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>46105</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>46105</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>46105</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>46104</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45951</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45953</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45812</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45357</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45727</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44966</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45034</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45617</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>45960</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45359</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45020</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>46125</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>46125</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45951</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45967</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45967</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44994</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44851</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45357</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45357</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45468</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>46126</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>45978</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45980</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45645</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45980</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45980</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45141</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45982</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45159</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45552</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45379</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45184</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44482</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>45993</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45839</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45924</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>45076</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>46000</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>46000</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45028</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45182</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45653</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45691</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>44477</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>46000</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>46006</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>46006</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>45819</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45033</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45824</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45772</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>45769</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>44606</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45016</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45076</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>46147</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45028</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45831</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45086</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45236</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>45089</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45183</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45978</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45198</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45838</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45110</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45007</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45384</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44900</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>45077</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45077</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>44481</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>44959</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45379</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45122</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45688</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>45198</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>46170</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>46171</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>45159</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>46176</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>46176</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>44959</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>45304</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45343</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>45161</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45468</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>45707</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45552</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45593</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45126</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>46184</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>46185</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>46185</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>46185</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45600</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45616</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>46184</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45161</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>44578</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>46184</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45356</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45572</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45124</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>46195</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>46195</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45126</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45000</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45357</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>46196</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45068</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45084</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>45616</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45316</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>45610</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>45009</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>45364</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>44705</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>45372</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45372</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>46254</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45665</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>46254</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>44705</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>45146</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>46255</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>44678</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>46214</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>46214</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>46214</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44623</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>45404</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>45586</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44700</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44671</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44739</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>44721</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45159</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>46265</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>46265</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>46224</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45762</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>46265</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45775</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>46267</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45300</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45769</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45304</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45365</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>46273</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>45763</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>46273</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44847</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44482</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45393</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>45365</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45365</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45574</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>46283</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>46286</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>46286</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>44524</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44565</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>44985</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>44952</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>44957</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>45148</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44888</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45363</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45365</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45553</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45300</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>45184</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45372</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>44620</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44985</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>44981</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>45665</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45359</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45146</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45363</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45378</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45033</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44978</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45412</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>45097</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>45365</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>45408</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>45077</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>45537</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>45357</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>45775</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45001</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45698</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45594</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45201</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>45398</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>44603</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44848</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>44886</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>45063</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>44475</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45546</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>44886</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45069</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45135</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>44886</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>44886</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45702</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>46029</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>46135</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>

--- a/Översikt ANEBY.xlsx
+++ b/Översikt ANEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45293</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45109</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44886</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>45202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44565</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>45393</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45792</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>46126</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>45996</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>45539</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45912</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>46072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>45293</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>46283</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>45365</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45709</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>46283</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45205</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>46184</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44677</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44508</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45461</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3798,7 +3798,7 @@
         <v>45547</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         <v>45558</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>45386</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4117,7 +4117,7 @@
         <v>45936</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         <v>44747</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45161</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4432,7 +4432,7 @@
         <v>44565</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45229</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         <v>46176</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4747,7 +4747,7 @@
         <v>46174</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>45365</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>44740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>46268</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>44985</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45707</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>45467</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>44533</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>44532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>44739</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>44888</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>44747</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>44743</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44539</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44853</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44585</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44853</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>44624</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44621</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44826</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>44739</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44739</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>44606</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44606</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44888</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44886</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44565</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>44503</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>45033</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45771</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7549,7 +7549,7 @@
         <v>45189</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>45749</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7695,7 +7695,7 @@
         <v>45107</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7768,7 +7768,7 @@
         <v>45205</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>45092</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>45419</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45460</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45250</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45393</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45393</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45461</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44860</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>44957</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>46020</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         <v>44852</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8654,7 +8654,7 @@
         <v>46021</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8727,7 +8727,7 @@
         <v>46021</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8800,7 +8800,7 @@
         <v>45796</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>45454</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         <v>46030</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         <v>45356</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9092,7 +9092,7 @@
         <v>45330</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45205</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9243,7 +9243,7 @@
         <v>45840</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>45608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9389,7 +9389,7 @@
         <v>46035</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44890</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>44890</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         <v>45889</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
         <v>45275</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9754,7 +9754,7 @@
         <v>45467</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45889</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45156</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>44550</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>45475</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10139,7 +10139,7 @@
         <v>46045</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>45903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>45665</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>45908</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>46051</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45909</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>44859</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10660,7 +10660,7 @@
         <v>45909</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45439</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>44999</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10884,7 +10884,7 @@
         <v>46056</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10957,7 +10957,7 @@
         <v>45912</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11030,7 +11030,7 @@
         <v>46057</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11103,7 +11103,7 @@
         <v>46058</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>46058</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>46057</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11322,7 +11322,7 @@
         <v>46057</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11395,7 +11395,7 @@
         <v>46030</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11468,7 +11468,7 @@
         <v>45911</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11546,7 +11546,7 @@
         <v>46059</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11619,7 +11619,7 @@
         <v>46064</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>45555</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11765,7 +11765,7 @@
         <v>45531</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>45924</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>46076</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>46073</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12057,7 +12057,7 @@
         <v>45358</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12135,7 +12135,7 @@
         <v>46084</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         <v>45936</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>46090</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44888</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>46093</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>45586</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12578,7 +12578,7 @@
         <v>46098</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12656,7 +12656,7 @@
         <v>45539</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12729,7 +12729,7 @@
         <v>45946</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>46104</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12875,7 +12875,7 @@
         <v>46105</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>46105</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>46105</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13094,7 +13094,7 @@
         <v>46104</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>45951</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13240,7 +13240,7 @@
         <v>45953</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>45812</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13386,7 +13386,7 @@
         <v>45357</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>45727</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44966</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>45034</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>45617</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13756,7 +13756,7 @@
         <v>45960</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>45359</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13902,7 +13902,7 @@
         <v>45020</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13975,7 +13975,7 @@
         <v>46125</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>46125</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45951</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>45967</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45967</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44994</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>44851</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45357</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45357</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>45468</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>46126</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14778,7 +14778,7 @@
         <v>45978</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14856,7 +14856,7 @@
         <v>45980</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14929,7 +14929,7 @@
         <v>45645</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15002,7 +15002,7 @@
         <v>45980</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45980</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15148,7 +15148,7 @@
         <v>45141</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15221,7 +15221,7 @@
         <v>45982</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15294,7 +15294,7 @@
         <v>45159</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>45552</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45379</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45184</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>44482</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>45993</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15732,7 +15732,7 @@
         <v>45839</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>45924</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>45076</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>46000</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>46000</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16097,7 +16097,7 @@
         <v>45028</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>45182</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16243,7 +16243,7 @@
         <v>45653</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>45691</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16389,7 +16389,7 @@
         <v>44477</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16462,7 +16462,7 @@
         <v>46000</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16535,7 +16535,7 @@
         <v>46006</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16608,7 +16608,7 @@
         <v>46006</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16681,7 +16681,7 @@
         <v>45819</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>45033</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>45824</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45772</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>45769</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
         <v>44606</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17124,7 +17124,7 @@
         <v>45016</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>45076</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17270,7 +17270,7 @@
         <v>46147</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>45028</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>45831</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>45086</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>45236</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>45089</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>45183</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
         <v>45978</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17859,7 +17859,7 @@
         <v>45198</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>45838</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45110</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45007</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45384</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>44900</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>45077</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45077</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>44481</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>44959</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>45379</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>45122</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>45688</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>45198</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>46170</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18969,7 +18969,7 @@
         <v>46171</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19042,7 +19042,7 @@
         <v>45159</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>46176</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19188,7 +19188,7 @@
         <v>46176</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>44959</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19334,7 +19334,7 @@
         <v>45304</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>45343</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19480,7 +19480,7 @@
         <v>45161</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>45468</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19631,7 +19631,7 @@
         <v>45707</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19704,7 +19704,7 @@
         <v>45552</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19777,7 +19777,7 @@
         <v>45593</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19850,7 +19850,7 @@
         <v>45126</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>46184</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20001,7 +20001,7 @@
         <v>46185</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20079,7 +20079,7 @@
         <v>46185</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20157,7 +20157,7 @@
         <v>46185</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>45600</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>45616</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>46184</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45161</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20532,7 +20532,7 @@
         <v>44578</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20605,7 +20605,7 @@
         <v>46184</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20678,7 +20678,7 @@
         <v>45356</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20751,7 +20751,7 @@
         <v>45572</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45124</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>46195</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20975,7 +20975,7 @@
         <v>46195</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45126</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45000</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45357</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>46196</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45068</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45084</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>45616</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45316</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>45610</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>45009</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>45364</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>44705</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>45372</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45372</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>46254</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45665</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>46254</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22304,7 +22304,7 @@
         <v>44705</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>45146</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>46255</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>44678</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>46214</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22674,7 +22674,7 @@
         <v>46214</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22747,7 +22747,7 @@
         <v>46214</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22820,7 +22820,7 @@
         <v>44623</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>45404</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22966,7 +22966,7 @@
         <v>45586</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>44700</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>44671</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>44739</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>44721</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23341,7 +23341,7 @@
         <v>45159</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23414,7 +23414,7 @@
         <v>46265</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23487,7 +23487,7 @@
         <v>46265</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>46224</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45762</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23711,7 +23711,7 @@
         <v>46265</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23784,7 +23784,7 @@
         <v>45775</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23862,7 +23862,7 @@
         <v>46267</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23935,7 +23935,7 @@
         <v>45300</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24008,7 +24008,7 @@
         <v>45769</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45304</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24154,7 +24154,7 @@
         <v>45365</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24232,7 +24232,7 @@
         <v>46273</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24305,7 +24305,7 @@
         <v>45763</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>46273</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>44847</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24529,7 +24529,7 @@
         <v>44482</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24602,7 +24602,7 @@
         <v>45393</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24675,7 +24675,7 @@
         <v>45365</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24753,7 +24753,7 @@
         <v>45365</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24831,7 +24831,7 @@
         <v>45574</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24904,7 +24904,7 @@
         <v>46283</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>46286</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25050,7 +25050,7 @@
         <v>46286</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25123,7 +25123,7 @@
         <v>44524</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25196,7 +25196,7 @@
         <v>44565</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>44985</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25342,7 +25342,7 @@
         <v>44952</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25415,7 +25415,7 @@
         <v>44957</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25488,7 +25488,7 @@
         <v>45148</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>44888</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>45363</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45365</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25785,7 +25785,7 @@
         <v>45553</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25858,7 +25858,7 @@
         <v>45300</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25931,7 +25931,7 @@
         <v>45184</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26004,7 +26004,7 @@
         <v>45372</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>44620</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>44985</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>44981</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>45665</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26379,7 +26379,7 @@
         <v>45359</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45146</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45363</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26598,7 +26598,7 @@
         <v>45378</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26671,7 +26671,7 @@
         <v>45033</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26744,7 +26744,7 @@
         <v>44978</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26817,7 +26817,7 @@
         <v>45412</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>45097</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26963,7 +26963,7 @@
         <v>45365</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>45408</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>45077</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>45537</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27260,7 +27260,7 @@
         <v>45357</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>45775</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45001</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>45698</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45594</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>45201</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>45398</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>44603</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27849,7 +27849,7 @@
         <v>44848</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27922,7 +27922,7 @@
         <v>44886</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27995,7 +27995,7 @@
         <v>45063</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         <v>44475</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28141,7 +28141,7 @@
         <v>45546</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28214,7 +28214,7 @@
         <v>44886</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28287,7 +28287,7 @@
         <v>45069</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45135</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28433,7 +28433,7 @@
         <v>44886</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>44886</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>45702</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>46029</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>46135</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>

--- a/Översikt ANEBY.xlsx
+++ b/Översikt ANEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45293</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45109</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44886</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>45202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44565</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>45393</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45792</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45539</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>45996</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45912</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>45293</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>46072</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45709</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>46283</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45365</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>46283</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45205</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>46184</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44677</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44508</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>44747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>45936</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45558</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>45467</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45707</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45461</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45365</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44985</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>44740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44565</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>45547</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45386</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>46174</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>46176</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>45161</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>46268</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>44533</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>44532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>44739</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>44888</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>44747</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>44743</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44539</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44853</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44585</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44853</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>44624</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44621</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44826</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>44739</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44739</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>44826</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44606</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44606</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44888</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44886</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44565</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>44503</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>44959</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45419</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45775</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>45359</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44888</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45617</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>45007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45468</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45107</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45126</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45182</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45033</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45769</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45769</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>45365</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45122</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44985</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>44888</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>44847</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>45028</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>46000</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45384</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>46006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>45594</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>44852</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>46006</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>45665</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45201</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>45205</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45363</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45608</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45398</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>45889</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>45889</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>45840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>46020</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>46021</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>45762</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>46021</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45300</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45727</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45653</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>46030</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>45461</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>46035</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45903</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45141</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45250</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45908</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45909</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>45909</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45236</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>46045</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>45912</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45796</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>45531</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>46051</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>45439</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45300</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>44678</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45183</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45924</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45304</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>46056</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>46057</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>46057</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>46030</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>46057</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>46058</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>46059</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>46058</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45475</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45146</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46064</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45553</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45936</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44860</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>44482</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45020</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>46073</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>45358</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>45330</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>46076</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45946</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>45951</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>46084</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>45953</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>46090</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>45960</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45357</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>46093</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45951</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45086</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45967</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45967</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>46098</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45124</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45539</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>46104</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>46104</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>44482</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45148</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>44481</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45819</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>46105</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45359</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45978</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>46105</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>46105</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45980</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45980</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45980</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45982</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45749</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45824</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45993</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>46125</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45691</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>46125</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>46126</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>46000</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>46000</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45159</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>45831</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45552</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45356</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45552</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45838</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45189</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45572</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>44477</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45688</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45771</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45924</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>44606</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45393</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45000</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>44985</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45839</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>45454</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>44705</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45537</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45097</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45665</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45379</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45146</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>46147</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>44739</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45412</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45357</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>45645</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45372</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>45357</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44952</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45707</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44550</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45978</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>44623</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>45076</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45198</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45393</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45467</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45068</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>45033</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>45077</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>45077</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45198</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>46170</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>46171</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45159</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>46176</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20210,7 +20210,7 @@
         <v>46176</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44705</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>45610</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44721</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>45616</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>46185</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>46185</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>46185</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>46184</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>46184</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>46184</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45772</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>45316</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>46195</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>46195</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44966</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>46196</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45184</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>44999</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45084</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>45665</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>44957</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>45275</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>45009</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45343</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>45304</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>46214</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>46214</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>46214</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44578</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45468</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>45593</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>46265</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>44890</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>46265</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44890</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>46265</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45364</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45393</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>44859</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>46267</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45763</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>44851</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>46224</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45372</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>46273</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44620</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>46273</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>44981</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45379</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>45126</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>44671</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>46283</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45356</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45365</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45365</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>46286</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>46286</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45110</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45365</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>44959</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45034</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>45574</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>44524</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45033</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44900</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45076</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45460</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>45156</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>45363</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>45077</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>45092</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45161</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>46294</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45028</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>45616</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45408</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>45016</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>46254</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44978</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>46254</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>46255</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45372</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45378</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44994</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45555</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45184</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>44957</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44700</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45159</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45357</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45357</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45089</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45404</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45365</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>45600</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45161</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44565</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45775</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45001</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45698</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44848</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>44886</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>45063</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44475</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>45546</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44886</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45069</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45135</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44603</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44886</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>44886</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>45702</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>46029</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>46135</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>

--- a/Översikt ANEBY.xlsx
+++ b/Översikt ANEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45293</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45109</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44886</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1232,7 +1232,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>45202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>44565</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1594,7 +1594,7 @@
         <v>45393</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1708,7 +1708,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1822,7 +1822,7 @@
         <v>45792</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1931,7 +1931,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
         <v>45539</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2269,7 +2269,7 @@
         <v>45996</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2381,7 +2381,7 @@
         <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45912</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         <v>45293</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         <v>46072</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>45709</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>46283</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>45365</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>46283</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>45205</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>46184</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>44677</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>44508</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>44747</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>45936</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45558</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>45467</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45707</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45461</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         <v>45365</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>44985</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>44740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>44565</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>45547</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>45386</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>46174</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>46176</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5181,7 +5181,7 @@
         <v>45161</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
         <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5391,7 +5391,7 @@
         <v>46268</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5500,7 +5500,7 @@
         <v>44533</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>44532</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5646,7 +5646,7 @@
         <v>44739</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         <v>44550</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>44888</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>44747</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5943,7 +5943,7 @@
         <v>44743</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44539</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>44853</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44585</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>44853</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>44624</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
         <v>44621</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         <v>44826</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
         <v>44739</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>44739</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6746,7 +6746,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         <v>44826</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>44606</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44606</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>44888</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44886</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44565</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>44606</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>44503</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>44959</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45419</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>45775</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7632,7 +7632,7 @@
         <v>45359</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         <v>44888</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45617</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7851,7 +7851,7 @@
         <v>45007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7924,7 +7924,7 @@
         <v>45468</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7997,7 +7997,7 @@
         <v>45107</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>45126</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45182</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45033</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45769</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>45769</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>45365</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>45122</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44985</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8659,7 +8659,7 @@
         <v>44888</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>44847</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8805,7 +8805,7 @@
         <v>45028</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8878,7 +8878,7 @@
         <v>46000</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         <v>45384</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9024,7 +9024,7 @@
         <v>46006</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9097,7 +9097,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>45594</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>44852</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>46006</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>45665</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>45201</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>45205</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9623,7 +9623,7 @@
         <v>45363</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         <v>45608</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9769,7 +9769,7 @@
         <v>45398</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>45889</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9915,7 +9915,7 @@
         <v>45889</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9988,7 +9988,7 @@
         <v>45840</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>46020</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
         <v>46021</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10207,7 +10207,7 @@
         <v>45762</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10285,7 +10285,7 @@
         <v>46021</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>45300</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10431,7 +10431,7 @@
         <v>45727</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45653</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         <v>46030</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>45461</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         <v>46035</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>45903</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10869,7 +10869,7 @@
         <v>45141</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10942,7 +10942,7 @@
         <v>45250</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11015,7 +11015,7 @@
         <v>45908</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11088,7 +11088,7 @@
         <v>45909</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11161,7 +11161,7 @@
         <v>45909</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11234,7 +11234,7 @@
         <v>45236</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11307,7 +11307,7 @@
         <v>46045</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11380,7 +11380,7 @@
         <v>45911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11458,7 +11458,7 @@
         <v>45912</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>45796</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11604,7 +11604,7 @@
         <v>45531</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11677,7 +11677,7 @@
         <v>46051</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>45439</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
         <v>45300</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11901,7 +11901,7 @@
         <v>44678</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11974,7 +11974,7 @@
         <v>45183</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12047,7 +12047,7 @@
         <v>45924</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12120,7 +12120,7 @@
         <v>45304</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12193,7 +12193,7 @@
         <v>46056</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
         <v>46057</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12339,7 +12339,7 @@
         <v>46057</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>46030</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12485,7 +12485,7 @@
         <v>46057</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12558,7 +12558,7 @@
         <v>46058</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>46059</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12704,7 +12704,7 @@
         <v>46058</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45475</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45146</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46064</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45553</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45936</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>44860</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>44482</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13288,7 +13288,7 @@
         <v>45020</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13361,7 +13361,7 @@
         <v>46073</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13434,7 +13434,7 @@
         <v>45358</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13512,7 +13512,7 @@
         <v>45330</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>46076</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>45946</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13731,7 +13731,7 @@
         <v>45812</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>45951</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>46084</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>45953</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>46090</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>45960</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14169,7 +14169,7 @@
         <v>45357</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14242,7 +14242,7 @@
         <v>46093</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14315,7 +14315,7 @@
         <v>45951</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14388,7 +14388,7 @@
         <v>45086</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45967</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45967</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>46098</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>45124</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>45539</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>46104</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>46104</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14977,7 +14977,7 @@
         <v>44482</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         <v>45148</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>44481</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>45819</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>46105</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45359</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45978</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15493,7 +15493,7 @@
         <v>46105</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>46105</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>45980</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>45980</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15785,7 +15785,7 @@
         <v>45980</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
         <v>45982</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>45749</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16004,7 +16004,7 @@
         <v>45824</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>45993</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16155,7 +16155,7 @@
         <v>46125</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16228,7 +16228,7 @@
         <v>45691</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16301,7 +16301,7 @@
         <v>46125</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16374,7 +16374,7 @@
         <v>46126</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>46000</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>46000</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>45159</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16666,7 +16666,7 @@
         <v>45831</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>45552</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>45356</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>45552</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>45838</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17036,7 +17036,7 @@
         <v>45189</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>45572</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17182,7 +17182,7 @@
         <v>44477</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
         <v>45688</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45771</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17401,7 +17401,7 @@
         <v>45924</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>44606</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>45393</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17620,7 +17620,7 @@
         <v>45000</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>44985</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>45839</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17839,7 +17839,7 @@
         <v>45454</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17912,7 +17912,7 @@
         <v>44705</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45537</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45097</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>45665</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18209,7 +18209,7 @@
         <v>45379</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45146</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18355,7 +18355,7 @@
         <v>46147</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18428,7 +18428,7 @@
         <v>44739</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18501,7 +18501,7 @@
         <v>45412</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18574,7 +18574,7 @@
         <v>45357</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18647,7 +18647,7 @@
         <v>45645</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18720,7 +18720,7 @@
         <v>45372</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>45357</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18866,7 +18866,7 @@
         <v>44952</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18939,7 +18939,7 @@
         <v>45707</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44550</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45978</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>44623</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>45076</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>45198</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19382,7 +19382,7 @@
         <v>45393</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19455,7 +19455,7 @@
         <v>45467</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19548,7 +19548,7 @@
         <v>45068</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19621,7 +19621,7 @@
         <v>45033</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
         <v>45077</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19767,7 +19767,7 @@
         <v>45077</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45198</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19918,7 +19918,7 @@
         <v>46170</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>46171</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20064,7 +20064,7 @@
         <v>45159</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20137,7 +20137,7 @@
         <v>46176</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20210,7 +20210,7 @@
         <v>46176</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20283,7 +20283,7 @@
         <v>44705</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
         <v>45610</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20429,7 +20429,7 @@
         <v>44721</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20502,7 +20502,7 @@
         <v>45616</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>46185</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>46185</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>46185</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20809,7 +20809,7 @@
         <v>46184</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
         <v>46184</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20960,7 +20960,7 @@
         <v>46184</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21038,7 +21038,7 @@
         <v>45772</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21111,7 +21111,7 @@
         <v>45316</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21184,7 +21184,7 @@
         <v>46195</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>46195</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>44966</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>46196</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45184</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>44999</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45084</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>45665</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>44957</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>45275</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>45009</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45343</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>45304</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>46214</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>46214</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>46214</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22372,7 +22372,7 @@
         <v>44578</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22445,7 +22445,7 @@
         <v>45468</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22518,7 +22518,7 @@
         <v>45593</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22591,7 +22591,7 @@
         <v>46265</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>44890</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>46265</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22810,7 +22810,7 @@
         <v>44890</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>46265</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45364</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23029,7 +23029,7 @@
         <v>45393</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23102,7 +23102,7 @@
         <v>44859</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>46267</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>45763</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23331,7 +23331,7 @@
         <v>44851</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23404,7 +23404,7 @@
         <v>46224</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23477,7 +23477,7 @@
         <v>45372</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>46273</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23623,7 +23623,7 @@
         <v>44620</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23696,7 +23696,7 @@
         <v>46273</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23769,7 +23769,7 @@
         <v>44981</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23847,7 +23847,7 @@
         <v>45379</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23920,7 +23920,7 @@
         <v>45126</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23993,7 +23993,7 @@
         <v>44671</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>46283</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45356</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45365</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45365</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24373,7 +24373,7 @@
         <v>46286</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24446,7 +24446,7 @@
         <v>46286</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24519,7 +24519,7 @@
         <v>45110</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24592,7 +24592,7 @@
         <v>45365</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24670,7 +24670,7 @@
         <v>44959</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45034</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>45574</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24894,7 +24894,7 @@
         <v>44524</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24967,7 +24967,7 @@
         <v>45033</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44900</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25118,7 +25118,7 @@
         <v>45076</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25191,7 +25191,7 @@
         <v>45460</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25264,7 +25264,7 @@
         <v>45156</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         <v>45363</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25410,7 +25410,7 @@
         <v>45077</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25483,7 +25483,7 @@
         <v>45092</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>45161</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25634,7 +25634,7 @@
         <v>46294</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>45028</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25780,7 +25780,7 @@
         <v>45616</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25853,7 +25853,7 @@
         <v>45408</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25926,7 +25926,7 @@
         <v>45016</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25999,7 +25999,7 @@
         <v>46254</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>44978</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>46254</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>46255</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26296,7 +26296,7 @@
         <v>45372</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26369,7 +26369,7 @@
         <v>45378</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26442,7 +26442,7 @@
         <v>44994</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26515,7 +26515,7 @@
         <v>45555</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45184</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26661,7 +26661,7 @@
         <v>44957</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26734,7 +26734,7 @@
         <v>44700</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26807,7 +26807,7 @@
         <v>45159</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45357</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26953,7 +26953,7 @@
         <v>45357</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>45089</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27099,7 +27099,7 @@
         <v>45404</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27172,7 +27172,7 @@
         <v>45365</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>45600</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27323,7 +27323,7 @@
         <v>45161</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44565</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27469,7 +27469,7 @@
         <v>45775</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27547,7 +27547,7 @@
         <v>45001</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27620,7 +27620,7 @@
         <v>45698</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>44848</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27766,7 +27766,7 @@
         <v>44886</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>45063</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27912,7 +27912,7 @@
         <v>44475</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         <v>45546</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44886</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45069</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45135</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>44603</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28350,7 +28350,7 @@
         <v>44886</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>44886</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>45702</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>46029</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28642,7 +28642,7 @@
         <v>46135</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>

--- a/Översikt ANEBY.xlsx
+++ b/Översikt ANEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45293</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45109</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44886</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>45202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44565</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45393</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45792</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>45539</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>45996</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45912</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45293</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45365</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45709</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>46072</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>46283</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46300</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>46283</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44677</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>45205</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>46184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44508</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45461</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45707</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>45467</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45365</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45547</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45386</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45936</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>45558</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45161</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44565</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>45229</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>46176</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46174</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>46268</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44533</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44739</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44550</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44747</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44743</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44539</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44853</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44624</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44585</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44739</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>44739</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44739</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>44565</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44888</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44606</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44853</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44886</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>44606</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>44624</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>44621</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>44826</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44985</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44503</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45028</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45205</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>45092</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>45086</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>45236</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>44981</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>45665</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>45033</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45771</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45089</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>45183</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45359</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45419</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>45460</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>45189</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>45110</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>45007</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>45384</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>44900</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>45250</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45077</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45077</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44481</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45393</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45393</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45146</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44959</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45363</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45379</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45461</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45122</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44860</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45378</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44705</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45033</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44957</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44852</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45205</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>44978</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45454</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45412</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45840</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45608</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45097</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45889</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45365</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>45159</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45356</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>45408</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>45330</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>44959</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>45889</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45077</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44890</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44890</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>45275</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>45467</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>45156</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45304</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>45343</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>45903</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45161</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>45908</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44550</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45357</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45909</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45468</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45909</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45475</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45775</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45912</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45707</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45552</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>45665</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>45911</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>45593</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44859</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45001</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45126</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44999</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45600</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45698</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45616</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>45161</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44578</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>45555</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45924</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45356</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45572</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45124</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45594</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45201</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45398</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45126</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>45000</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45358</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45796</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45357</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45068</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45084</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44888</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>45616</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45316</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45610</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45936</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>45364</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>45372</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>45372</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>45812</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45665</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45946</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45357</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>45727</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44966</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>44705</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>45146</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45034</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45617</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45819</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>44678</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45359</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45824</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45020</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45951</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44623</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44994</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44851</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45357</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>45357</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>45404</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45831</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45953</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45468</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45960</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>44700</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45838</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44671</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45645</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44739</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45141</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>44721</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45951</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45967</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45159</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45967</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45552</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45379</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45159</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45184</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45762</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>45688</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44482</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45076</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45775</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45300</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>45769</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>45028</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>45182</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>45653</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>45691</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45978</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45304</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45980</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45980</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45033</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45365</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45763</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>45980</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>44847</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45982</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>46098</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45539</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>45772</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>46104</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>44482</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>46105</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46105</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>46105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45769</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46104</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>44606</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45393</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45365</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45365</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45574</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45016</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45076</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45993</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>44524</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44565</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>46125</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>46125</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>46000</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>46000</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>44985</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>46126</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44952</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>46000</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>46006</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46006</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44957</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45148</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>44888</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45839</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45924</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>46020</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45363</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>46021</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>46021</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45365</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>45553</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>46030</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>45300</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>45184</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45372</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>46035</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44620</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>46045</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>46051</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45439</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>46056</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>46057</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>46058</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>46058</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>46057</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>46057</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>46030</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>46059</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>46064</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>46147</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>46076</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>46073</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>46084</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>46090</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45978</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45198</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>46093</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>45198</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>46170</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>46171</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>46176</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>46176</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>46184</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>46185</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>46185</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>46185</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>46184</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46184</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>46195</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>46195</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>46196</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45009</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>46214</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>46214</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>46214</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>46265</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>46265</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>46224</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46265</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>46267</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>46273</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>46273</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>46283</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>46286</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>46286</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>46294</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>46254</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>46300</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>46254</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>46255</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>46302</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46302</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>46302</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44603</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44848</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44886</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45063</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45546</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>44886</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45069</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45135</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44886</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44886</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45702</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>46029</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>46135</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>

--- a/Översikt ANEBY.xlsx
+++ b/Översikt ANEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45293</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45109</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44886</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>45202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44565</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45393</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45792</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>45539</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>45996</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>45912</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45293</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45365</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45709</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2938,7 +2938,7 @@
         <v>46072</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>46283</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46300</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>46283</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44677</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>45205</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>46184</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44508</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44985</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45461</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4017,7 +4017,7 @@
         <v>45707</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>45467</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45365</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45547</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4450,7 +4450,7 @@
         <v>45386</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45936</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4660,7 +4660,7 @@
         <v>45558</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4765,7 +4765,7 @@
         <v>44747</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45161</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         <v>44565</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         <v>45229</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>46176</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5395,7 +5395,7 @@
         <v>46174</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>46268</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44533</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44739</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44550</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44747</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44743</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44539</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44853</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44624</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44585</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44739</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>44739</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44739</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>44565</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44888</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44606</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44853</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44886</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>44606</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>44624</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>44621</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>44826</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44985</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44503</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45028</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7663,7 +7663,7 @@
         <v>45107</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>45205</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>45092</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7887,7 +7887,7 @@
         <v>45086</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>45236</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>44981</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>45665</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8189,7 +8189,7 @@
         <v>45033</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         <v>45771</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         <v>45089</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8408,7 +8408,7 @@
         <v>45183</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8481,7 +8481,7 @@
         <v>45359</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45419</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8632,7 +8632,7 @@
         <v>45460</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>45189</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         <v>45110</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>45007</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8924,7 +8924,7 @@
         <v>45384</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8997,7 +8997,7 @@
         <v>44900</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9075,7 +9075,7 @@
         <v>45250</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9148,7 +9148,7 @@
         <v>45077</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45077</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>44481</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45393</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9440,7 +9440,7 @@
         <v>45393</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45146</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44959</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>45363</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45379</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>45749</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>45461</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45122</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44860</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45378</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44705</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45033</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44957</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10389,7 +10389,7 @@
         <v>44852</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>45205</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>44978</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45454</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10686,7 +10686,7 @@
         <v>45412</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>45840</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>45608</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10905,7 +10905,7 @@
         <v>45097</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>45889</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>45365</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>45159</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45356</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>45408</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>45330</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>44959</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>45889</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45077</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11640,7 +11640,7 @@
         <v>44890</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         <v>44890</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>45275</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>45467</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>45156</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12025,7 +12025,7 @@
         <v>45304</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>45343</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12171,7 +12171,7 @@
         <v>45903</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45161</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>45537</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>45908</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44550</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>45357</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         <v>45909</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45468</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>45909</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12833,7 +12833,7 @@
         <v>45475</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>45775</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12984,7 +12984,7 @@
         <v>45912</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13057,7 +13057,7 @@
         <v>45707</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45552</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>45665</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13281,7 +13281,7 @@
         <v>45911</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
         <v>45593</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>44859</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45001</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45126</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>44999</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45600</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>45698</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45616</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>45161</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>44578</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>45555</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45924</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45356</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45572</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45124</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45594</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45201</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45398</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45126</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>45000</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>45358</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45796</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45357</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45068</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
         <v>45084</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44888</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>45616</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15340,7 +15340,7 @@
         <v>45316</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15413,7 +15413,7 @@
         <v>45610</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15486,7 +15486,7 @@
         <v>45936</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>45364</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15632,7 +15632,7 @@
         <v>45531</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15705,7 +15705,7 @@
         <v>45372</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15778,7 +15778,7 @@
         <v>45372</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>45812</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>45665</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>45946</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16075,7 +16075,7 @@
         <v>45357</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16148,7 +16148,7 @@
         <v>45727</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16221,7 +16221,7 @@
         <v>44966</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16294,7 +16294,7 @@
         <v>44705</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         <v>45146</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16440,7 +16440,7 @@
         <v>45034</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45617</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>45819</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>44678</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45359</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45824</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>45020</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45951</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>44623</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17107,7 +17107,7 @@
         <v>44994</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44851</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45357</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17326,7 +17326,7 @@
         <v>45357</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17399,7 +17399,7 @@
         <v>45404</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45831</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17550,7 +17550,7 @@
         <v>45953</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45468</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17696,7 +17696,7 @@
         <v>45960</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17769,7 +17769,7 @@
         <v>44700</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17842,7 +17842,7 @@
         <v>45838</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17915,7 +17915,7 @@
         <v>44671</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17993,7 +17993,7 @@
         <v>45645</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>44739</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18139,7 +18139,7 @@
         <v>45141</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18212,7 +18212,7 @@
         <v>44721</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18285,7 +18285,7 @@
         <v>45951</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18358,7 +18358,7 @@
         <v>45967</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18431,7 +18431,7 @@
         <v>45159</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>45967</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45552</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18650,7 +18650,7 @@
         <v>45379</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18723,7 +18723,7 @@
         <v>45159</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         <v>45184</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18869,7 +18869,7 @@
         <v>45762</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>45688</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19020,7 +19020,7 @@
         <v>44482</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19093,7 +19093,7 @@
         <v>45076</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>45775</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45300</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19317,7 +19317,7 @@
         <v>45769</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>45028</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>45182</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>45653</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19609,7 +19609,7 @@
         <v>45691</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45978</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45304</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19833,7 +19833,7 @@
         <v>45980</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
         <v>45980</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19979,7 +19979,7 @@
         <v>45033</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45365</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45763</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20208,7 +20208,7 @@
         <v>45980</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20281,7 +20281,7 @@
         <v>44847</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45982</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>46098</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>45539</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>45772</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>46104</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
         <v>44482</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>46105</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46105</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>46105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>45769</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>46104</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>44606</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45393</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45365</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21386,7 +21386,7 @@
         <v>45365</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45574</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45016</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45076</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45993</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>44524</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>44565</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>46125</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>46125</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>46000</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>46000</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>44985</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>46126</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>44952</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>46000</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>46006</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46006</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>44957</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45148</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>44888</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45839</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45924</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>46020</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45363</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>46021</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>46021</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45365</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23367,7 +23367,7 @@
         <v>45553</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>46030</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>45300</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23586,7 +23586,7 @@
         <v>45184</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23659,7 +23659,7 @@
         <v>45372</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23732,7 +23732,7 @@
         <v>46035</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23805,7 +23805,7 @@
         <v>44620</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23878,7 +23878,7 @@
         <v>46045</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23951,7 +23951,7 @@
         <v>46051</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>45439</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>46056</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24175,7 +24175,7 @@
         <v>46057</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>46058</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>46058</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24394,7 +24394,7 @@
         <v>46057</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24467,7 +24467,7 @@
         <v>46057</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24540,7 +24540,7 @@
         <v>46030</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24613,7 +24613,7 @@
         <v>46059</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>46064</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>46147</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>46076</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>46073</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>46084</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>46090</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45978</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45198</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>46093</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>45198</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25426,7 +25426,7 @@
         <v>46170</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25499,7 +25499,7 @@
         <v>46171</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>46176</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>46176</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>46184</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25796,7 +25796,7 @@
         <v>46185</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>46185</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25952,7 +25952,7 @@
         <v>46185</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>46184</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46184</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>46195</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26259,7 +26259,7 @@
         <v>46195</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>46196</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>45009</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26488,7 +26488,7 @@
         <v>46214</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26561,7 +26561,7 @@
         <v>46214</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26634,7 +26634,7 @@
         <v>46214</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>46265</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>46265</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26853,7 +26853,7 @@
         <v>46224</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26926,7 +26926,7 @@
         <v>46265</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26999,7 +26999,7 @@
         <v>46267</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27072,7 +27072,7 @@
         <v>46273</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>46273</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>46283</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27291,7 +27291,7 @@
         <v>46286</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>46286</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27437,7 +27437,7 @@
         <v>46294</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27510,7 +27510,7 @@
         <v>46254</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>46300</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27656,7 +27656,7 @@
         <v>46254</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>46255</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>46302</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>46302</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>46302</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>44603</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44848</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44886</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45063</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45546</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>44886</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45069</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45135</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>44886</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44886</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28756,7 +28756,7 @@
         <v>45702</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28829,7 +28829,7 @@
         <v>46029</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28902,7 +28902,7 @@
         <v>46135</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>

--- a/Översikt ANEBY.xlsx
+++ b/Översikt ANEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45293</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45109</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44886</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>45202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44565</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45393</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45792</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>45996</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>45912</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45539</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45293</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45709</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>46072</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>46283</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45365</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46300</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>46283</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>45205</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>46184</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>44677</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44508</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45467</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>45707</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45461</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45365</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45936</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44985</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>44740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44565</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45547</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45386</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>46174</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46176</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>45161</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>45558</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>46268</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44533</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44739</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44550</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44747</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44743</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44539</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44853</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44585</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44853</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44624</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>44826</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>44624</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44739</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44739</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44826</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44606</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>44888</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>44886</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>44565</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>44606</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44959</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45419</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>45775</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>45359</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44888</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>45007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>45617</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>45468</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>45107</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>45182</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>45033</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45769</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45126</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44985</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45769</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44888</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45122</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>45365</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>44847</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>45384</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44852</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>45665</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45028</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45363</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45762</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45653</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45727</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45141</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45461</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45250</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45236</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45300</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>44678</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45183</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45304</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44860</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45553</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45475</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45330</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45020</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45358</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45357</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>45086</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>45124</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>45148</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45359</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>45749</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>45146</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45205</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45924</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>45691</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45608</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>45889</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45889</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45840</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44705</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45159</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>45839</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45552</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45903</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45356</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45552</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45908</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45909</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45909</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45189</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45911</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>45912</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45572</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46147</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45924</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45771</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45936</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44606</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45393</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45000</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44985</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45454</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45946</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44705</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>45951</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45953</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45960</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45537</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45951</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45967</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45967</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45097</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45978</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45665</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45379</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45198</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>45146</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>44739</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>45978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45412</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>45980</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>45357</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>45980</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>45980</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>45982</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45645</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45372</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45357</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>44952</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45707</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>44550</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45993</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>44623</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45076</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45393</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45198</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>45467</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>46000</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>45068</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>46000</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>46170</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>46000</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45033</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45077</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>45077</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>46006</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>46171</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>46006</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>45159</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>45610</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>46020</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>46021</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>46021</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         <v>44721</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>45616</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>46030</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>46035</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>46176</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>46176</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>46045</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         <v>45772</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>46051</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>45316</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45439</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>44966</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>46056</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>46057</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>46057</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>46030</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45184</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>46057</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>46058</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>44999</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>46059</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45084</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>46058</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>45665</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>46064</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>46185</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>46185</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>46185</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>46184</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>46073</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>46184</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>44957</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>46076</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45275</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>46184</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>46084</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>46090</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>45343</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45304</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>46093</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>44578</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>46098</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>46195</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45468</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45539</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>46104</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>46104</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>46195</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>46196</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45593</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46105</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>46105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46105</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>44890</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>44890</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45364</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45393</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>44859</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45763</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44851</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>46125</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>46125</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>46126</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45372</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>44620</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>44981</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45379</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45126</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45009</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44671</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45356</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>45365</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45365</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>46214</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>46214</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>46214</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>45110</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>46224</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45365</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>46273</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>44959</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45034</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>46273</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45574</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>44524</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45033</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44900</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45076</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>45460</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45156</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>45363</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45077</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45092</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45161</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45028</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45616</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>46283</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45408</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45016</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44978</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45372</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45378</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>44994</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45555</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>46286</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46286</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45184</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>44957</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44700</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45159</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45357</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45357</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45089</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45404</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45365</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>46294</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45600</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45161</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44565</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>46254</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>46254</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46255</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>45775</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>46300</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45001</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45698</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>46302</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>46302</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45594</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45201</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>46302</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>45398</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45796</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45531</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>46265</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>46265</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>46265</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45812</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>46267</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45819</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45824</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45831</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>45838</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>45688</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>44848</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>44886</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>45063</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>45546</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44886</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45069</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45135</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44603</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>44886</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>44886</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45702</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>46029</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>46135</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>

--- a/Översikt ANEBY.xlsx
+++ b/Översikt ANEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45293</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45109</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44886</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>45202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44565</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45393</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45792</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>45996</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>45912</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>46126</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2488,7 +2488,7 @@
         <v>45539</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45293</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45709</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>46072</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>46283</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45365</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46300</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>46283</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>45205</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3481,7 +3481,7 @@
         <v>46184</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>44677</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>44508</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>44747</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3908,7 +3908,7 @@
         <v>45467</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>45707</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45461</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         <v>45365</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4341,7 +4341,7 @@
         <v>45936</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>44985</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>44740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>44565</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4761,7 +4761,7 @@
         <v>45547</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>45386</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>46174</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>46176</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>45161</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45229</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>45558</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>46268</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         <v>44533</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44532</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>44739</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         <v>44550</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44888</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44747</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6057,7 +6057,7 @@
         <v>44743</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44539</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>44853</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44585</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6349,7 +6349,7 @@
         <v>44853</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         <v>44624</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6495,7 +6495,7 @@
         <v>44826</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         <v>44621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6641,7 +6641,7 @@
         <v>44624</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6714,7 +6714,7 @@
         <v>44739</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
         <v>44739</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44826</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>44606</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7152,7 +7152,7 @@
         <v>44888</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>44886</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7298,7 +7298,7 @@
         <v>44565</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>44606</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>44503</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>44959</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         <v>45419</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>45775</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>45359</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7819,7 +7819,7 @@
         <v>44888</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>45007</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
         <v>45617</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         <v>45468</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>45107</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8184,7 +8184,7 @@
         <v>45182</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>45033</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         <v>45769</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45126</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8476,7 +8476,7 @@
         <v>44985</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>45769</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>44888</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         <v>45122</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8768,7 +8768,7 @@
         <v>45365</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>44847</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         <v>45384</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8992,7 +8992,7 @@
         <v>44852</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>45665</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9143,7 +9143,7 @@
         <v>45205</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9221,7 +9221,7 @@
         <v>45028</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>45363</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45762</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45653</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45727</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45300</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45141</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45461</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45250</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>45236</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45300</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>44678</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10102,7 +10102,7 @@
         <v>45183</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45304</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10248,7 +10248,7 @@
         <v>44860</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>45553</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10394,7 +10394,7 @@
         <v>45475</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         <v>45330</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>45020</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45358</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45357</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>45086</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>45124</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>45148</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45359</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>45749</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>45146</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45205</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11280,7 +11280,7 @@
         <v>45924</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>45691</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45608</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>45889</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11572,7 +11572,7 @@
         <v>45889</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45840</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>44705</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>45159</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>45839</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45552</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45903</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45356</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>45552</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45908</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45909</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45909</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>45189</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>45911</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>45912</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45572</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>46147</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>45924</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45771</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45936</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>44606</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45393</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>45000</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>44985</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45454</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45946</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44705</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>45951</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>45953</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>45960</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45537</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45951</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>45967</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45967</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45097</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>45978</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45665</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45379</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45198</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14434,7 +14434,7 @@
         <v>45146</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         <v>44739</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>45978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45412</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>45980</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>45357</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>45980</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>45980</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>45982</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>45645</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45372</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>45357</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>44952</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>45707</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>44550</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45993</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>44623</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45076</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>45393</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45198</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15904,7 +15904,7 @@
         <v>45467</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>46000</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16070,7 +16070,7 @@
         <v>45068</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16143,7 +16143,7 @@
         <v>46000</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16216,7 +16216,7 @@
         <v>46170</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>46000</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16362,7 +16362,7 @@
         <v>45033</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>45077</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16508,7 +16508,7 @@
         <v>45077</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16581,7 +16581,7 @@
         <v>46006</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16654,7 +16654,7 @@
         <v>46171</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16727,7 +16727,7 @@
         <v>46006</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16800,7 +16800,7 @@
         <v>45159</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16873,7 +16873,7 @@
         <v>45610</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16946,7 +16946,7 @@
         <v>46020</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>46021</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17092,7 +17092,7 @@
         <v>46021</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17165,7 +17165,7 @@
         <v>44721</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17238,7 +17238,7 @@
         <v>45616</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>46030</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17384,7 +17384,7 @@
         <v>46035</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17457,7 +17457,7 @@
         <v>46176</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17530,7 +17530,7 @@
         <v>46176</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>46045</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17676,7 +17676,7 @@
         <v>45772</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>46051</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>45316</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17895,7 +17895,7 @@
         <v>45439</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17973,7 +17973,7 @@
         <v>44966</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>46056</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18119,7 +18119,7 @@
         <v>46057</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18192,7 +18192,7 @@
         <v>46057</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>46030</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18338,7 +18338,7 @@
         <v>45184</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18411,7 +18411,7 @@
         <v>46057</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18484,7 +18484,7 @@
         <v>46058</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>44999</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18630,7 +18630,7 @@
         <v>46059</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45084</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>46058</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18849,7 +18849,7 @@
         <v>45665</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18927,7 +18927,7 @@
         <v>46064</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19000,7 +19000,7 @@
         <v>46185</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>46185</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>46185</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19234,7 +19234,7 @@
         <v>46184</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19307,7 +19307,7 @@
         <v>46073</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>46184</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>44957</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19531,7 +19531,7 @@
         <v>46076</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19604,7 +19604,7 @@
         <v>45275</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>46184</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>46084</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19828,7 +19828,7 @@
         <v>46090</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19901,7 +19901,7 @@
         <v>45343</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19974,7 +19974,7 @@
         <v>45304</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>46093</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20120,7 +20120,7 @@
         <v>44578</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>46098</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>46195</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45468</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20422,7 +20422,7 @@
         <v>45539</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>46104</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20568,7 +20568,7 @@
         <v>46104</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20641,7 +20641,7 @@
         <v>46195</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20719,7 +20719,7 @@
         <v>46196</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20797,7 +20797,7 @@
         <v>45593</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20870,7 +20870,7 @@
         <v>46105</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>46105</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21016,7 +21016,7 @@
         <v>46105</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21089,7 +21089,7 @@
         <v>44890</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>44890</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21235,7 +21235,7 @@
         <v>45364</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45393</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>44859</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45763</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>44851</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>46125</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>46125</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>46126</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45372</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>44620</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>44981</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45379</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45126</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45009</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44671</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>45356</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>45365</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45365</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>46214</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>46214</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>46214</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>45110</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>46224</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22944,7 +22944,7 @@
         <v>45365</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>46273</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>44959</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>45034</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>46273</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45574</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>44524</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45033</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>44900</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23616,7 +23616,7 @@
         <v>45076</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23689,7 +23689,7 @@
         <v>45460</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23762,7 +23762,7 @@
         <v>45156</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>45363</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23908,7 +23908,7 @@
         <v>45077</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23981,7 +23981,7 @@
         <v>45092</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24054,7 +24054,7 @@
         <v>45161</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24132,7 +24132,7 @@
         <v>45028</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24205,7 +24205,7 @@
         <v>45616</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>46283</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24351,7 +24351,7 @@
         <v>45408</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24424,7 +24424,7 @@
         <v>45016</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24497,7 +24497,7 @@
         <v>44978</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45372</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45378</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>44994</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45555</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>46286</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>46286</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45184</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>44957</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44700</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45159</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45357</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45357</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45089</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>45404</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45365</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>46294</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45600</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25816,7 +25816,7 @@
         <v>45161</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25889,7 +25889,7 @@
         <v>44565</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>46254</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26035,7 +26035,7 @@
         <v>46254</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26108,7 +26108,7 @@
         <v>46255</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>45775</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>46300</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45001</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45698</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>46302</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>46302</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45594</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45201</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>46302</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>45398</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45796</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45531</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>46265</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>46265</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>46265</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45812</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>46267</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45819</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45824</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27583,7 +27583,7 @@
         <v>45831</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>45838</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27734,7 +27734,7 @@
         <v>45688</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>44848</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>44886</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>45063</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>45546</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28099,7 +28099,7 @@
         <v>44886</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>45069</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>45135</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44603</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>44886</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>44886</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>45702</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>46029</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>46135</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>

--- a/Översikt ANEBY.xlsx
+++ b/Översikt ANEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45293</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45109</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44886</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>45202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44565</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45393</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45792</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>45912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45996</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>45539</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46126</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45365</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45709</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>46283</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>46072</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>46300</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>45293</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>46283</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44677</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>46184</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>45205</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>46318</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>45936</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>46176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>46174</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>44985</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45461</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>45707</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45558</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>46268</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45547</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45386</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>45161</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>45229</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45365</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44533</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>44532</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>44739</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44888</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>44747</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44743</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44539</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>44853</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44585</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44853</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>44624</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>44826</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44624</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>44739</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44739</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>44826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44606</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44888</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44886</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44606</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45205</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44705</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>44503</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>45608</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>44957</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45889</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45033</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>45771</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>45889</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44888</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>45189</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45749</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>45363</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45903</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>45908</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>45365</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45978</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>45909</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>45198</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45909</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>45553</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>45300</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>45912</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>45911</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>45184</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>45372</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45198</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45924</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45107</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>45205</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>45092</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>46170</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>44620</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>46171</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>46176</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45936</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>46176</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45946</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45419</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>45460</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>45250</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45393</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45393</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>44981</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45665</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45951</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45461</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45359</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45953</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>46184</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>46185</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>46185</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>46185</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45960</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44860</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45146</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>46184</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45363</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>46184</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45951</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45967</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45967</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>46195</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>45378</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>46195</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>46196</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45033</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45978</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45980</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45980</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>44978</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45980</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>45412</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45097</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45982</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45009</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45365</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45408</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45077</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45993</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>46214</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>46214</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>46214</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>45537</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>46000</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>46000</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>45357</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>46224</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>45775</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>46000</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>46006</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44957</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>46006</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45001</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44852</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>45698</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>46020</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>46021</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>46021</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>46030</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45594</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>46283</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45201</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>46286</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>46286</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45398</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>46035</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45796</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>46045</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45454</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45531</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>46051</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45439</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>46056</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>46057</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>46058</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>46058</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>46057</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>46057</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>46030</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>46059</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45812</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>46064</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45819</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>46076</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>46073</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45824</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>46254</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         <v>46084</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>45831</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>46300</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45356</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>46254</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>46090</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>45838</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>46093</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>46098</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45539</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>45330</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>46255</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>46302</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>46104</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>46105</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>46105</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>46105</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>46104</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45688</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>46302</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>46302</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>44890</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>44890</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45275</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45467</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45156</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>46125</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>46125</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>46126</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>46265</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>46265</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>44550</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>46265</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45475</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45665</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>44859</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>44999</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>45839</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45924</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>46267</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45555</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46294</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>46273</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45358</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>46273</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>46317</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>46314</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>44888</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>46317</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>46317</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>46317</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>46147</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45357</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45727</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>44966</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45034</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45617</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45359</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45020</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>44994</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44851</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45357</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45357</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45468</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45645</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45141</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45159</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45552</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45379</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45184</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45076</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45028</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45182</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45653</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45691</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>45033</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45772</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45769</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44606</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>45016</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45076</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45028</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45086</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45236</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45089</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45183</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45110</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45007</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45384</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44900</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45077</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45077</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>44959</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45379</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45122</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45159</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>44959</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>45304</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45343</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45161</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45468</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45707</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45552</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45593</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45126</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45600</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>45616</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45161</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44578</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45356</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45572</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45124</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45126</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45000</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45357</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45068</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>45084</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45616</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>45316</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45610</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>45364</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>45372</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45372</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45665</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>44705</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>45146</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>44678</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44623</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45404</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44700</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44671</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>44739</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44721</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45159</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45762</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45775</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45300</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45769</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45304</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45365</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45763</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>44847</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45393</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45365</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45365</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>45574</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>44524</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44565</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44985</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>44952</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>44603</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44848</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44886</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45063</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45546</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44886</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45069</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45135</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>44886</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44886</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>45702</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>46029</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>46135</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>

--- a/Översikt ANEBY.xlsx
+++ b/Översikt ANEBY.xlsx
@@ -601,7 +601,7 @@
         <v>45293</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46161</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -869,7 +869,7 @@
         <v>45109</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>44886</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>46283</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45204</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>45202</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1478,7 +1478,7 @@
         <v>44565</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45393</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>44889</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>45792</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1934,7 +1934,7 @@
         <v>45712</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45964</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>45912</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2268,7 +2268,7 @@
         <v>45996</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         <v>45539</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2492,7 +2492,7 @@
         <v>46126</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>45365</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>45709</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>46283</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>46072</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         <v>46300</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>45293</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3263,7 +3263,7 @@
         <v>46283</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>44677</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         <v>46184</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3587,7 +3587,7 @@
         <v>45205</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3698,7 +3698,7 @@
         <v>46318</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3804,7 +3804,7 @@
         <v>44508</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3909,7 +3909,7 @@
         <v>45936</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4014,7 +4014,7 @@
         <v>46176</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>46174</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>44985</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>45461</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>45707</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>45467</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>45558</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         <v>46268</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>45547</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>45386</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>44747</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         <v>45161</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>44565</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>45229</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5505,7 +5505,7 @@
         <v>45365</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5615,7 +5615,7 @@
         <v>44740</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         <v>44533</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>44532</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>44739</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44550</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6017,7 +6017,7 @@
         <v>44888</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         <v>44747</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         <v>44743</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44539</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         <v>44853</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>44585</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>44853</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6528,7 +6528,7 @@
         <v>44624</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         <v>44621</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>44826</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>44624</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>44739</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>44739</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44739</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>44826</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>44606</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44606</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7258,7 +7258,7 @@
         <v>44888</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7331,7 +7331,7 @@
         <v>44886</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>44565</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7477,7 +7477,7 @@
         <v>44606</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45205</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         <v>44705</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
         <v>44503</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>45840</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7847,7 +7847,7 @@
         <v>45608</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7920,7 +7920,7 @@
         <v>44957</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45889</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45033</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         <v>45771</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
         <v>45889</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45148</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44888</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
         <v>45189</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8504,7 +8504,7 @@
         <v>45749</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8577,7 +8577,7 @@
         <v>45363</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45903</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>45908</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>45365</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>45978</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8947,7 +8947,7 @@
         <v>45909</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9020,7 +9020,7 @@
         <v>45198</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45909</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>45553</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>45300</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9317,7 +9317,7 @@
         <v>45912</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9390,7 +9390,7 @@
         <v>45911</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9468,7 +9468,7 @@
         <v>45184</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
         <v>45372</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>45198</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>45924</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9765,7 +9765,7 @@
         <v>45107</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>45205</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>45092</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9989,7 +9989,7 @@
         <v>46170</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>44620</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>46171</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10208,7 +10208,7 @@
         <v>46176</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>45936</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10354,7 +10354,7 @@
         <v>46176</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44985</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10500,7 +10500,7 @@
         <v>45946</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10573,7 +10573,7 @@
         <v>45419</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>45460</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>45250</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10797,7 +10797,7 @@
         <v>45393</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10870,7 +10870,7 @@
         <v>45393</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>44981</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         <v>45665</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11099,7 +11099,7 @@
         <v>45951</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11172,7 +11172,7 @@
         <v>45461</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11245,7 +11245,7 @@
         <v>45359</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11318,7 +11318,7 @@
         <v>45953</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>46184</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11469,7 +11469,7 @@
         <v>46185</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>46185</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>46185</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11703,7 +11703,7 @@
         <v>45960</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11776,7 +11776,7 @@
         <v>44860</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11849,7 +11849,7 @@
         <v>45146</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11922,7 +11922,7 @@
         <v>46184</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         <v>45363</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12073,7 +12073,7 @@
         <v>46184</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>45951</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12219,7 +12219,7 @@
         <v>45967</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>45967</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>46195</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12443,7 +12443,7 @@
         <v>45378</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12516,7 +12516,7 @@
         <v>46195</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>46196</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45033</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45978</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45980</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12896,7 +12896,7 @@
         <v>45980</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12969,7 +12969,7 @@
         <v>44978</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45980</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>45412</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>45097</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         <v>45982</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13334,7 +13334,7 @@
         <v>45009</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13407,7 +13407,7 @@
         <v>45365</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13485,7 +13485,7 @@
         <v>45408</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45077</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13631,7 +13631,7 @@
         <v>45993</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13704,7 +13704,7 @@
         <v>46214</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13777,7 +13777,7 @@
         <v>46214</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>46214</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13923,7 +13923,7 @@
         <v>45537</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>46000</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14069,7 +14069,7 @@
         <v>46000</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14142,7 +14142,7 @@
         <v>45357</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>46224</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>45775</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14366,7 +14366,7 @@
         <v>46000</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14439,7 +14439,7 @@
         <v>46006</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14512,7 +14512,7 @@
         <v>44957</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14585,7 +14585,7 @@
         <v>46006</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14658,7 +14658,7 @@
         <v>45001</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44852</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>45698</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>46020</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14950,7 +14950,7 @@
         <v>46021</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15023,7 +15023,7 @@
         <v>46021</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         <v>46030</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45594</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15242,7 +15242,7 @@
         <v>46283</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
         <v>45201</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>46286</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>46286</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15534,7 +15534,7 @@
         <v>45398</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15607,7 +15607,7 @@
         <v>46035</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15680,7 +15680,7 @@
         <v>45796</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15753,7 +15753,7 @@
         <v>46045</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15826,7 +15826,7 @@
         <v>45454</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15899,7 +15899,7 @@
         <v>45531</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15972,7 +15972,7 @@
         <v>46051</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16045,7 +16045,7 @@
         <v>45439</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>46056</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>46057</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         <v>46058</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16342,7 +16342,7 @@
         <v>46058</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16415,7 +16415,7 @@
         <v>46057</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>46057</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16561,7 +16561,7 @@
         <v>46030</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>46059</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16707,7 +16707,7 @@
         <v>45812</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16780,7 +16780,7 @@
         <v>46064</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16853,7 +16853,7 @@
         <v>45819</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>46076</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>46073</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17072,7 +17072,7 @@
         <v>45824</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>46254</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17223,7 +17223,7 @@
         <v>46084</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>45831</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>46300</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45356</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17520,7 +17520,7 @@
         <v>46254</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17593,7 +17593,7 @@
         <v>46090</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>45838</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>46093</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>46098</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45539</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17963,7 +17963,7 @@
         <v>45330</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18036,7 +18036,7 @@
         <v>46255</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
         <v>46302</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18187,7 +18187,7 @@
         <v>46104</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18260,7 +18260,7 @@
         <v>46105</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18333,7 +18333,7 @@
         <v>46105</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>46105</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>46104</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45688</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>46302</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18698,7 +18698,7 @@
         <v>46302</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18771,7 +18771,7 @@
         <v>44890</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>44890</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45275</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18990,7 +18990,7 @@
         <v>45467</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
         <v>45156</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19156,7 +19156,7 @@
         <v>46125</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>46125</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>46126</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>46265</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>46265</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19521,7 +19521,7 @@
         <v>44550</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19594,7 +19594,7 @@
         <v>46265</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19667,7 +19667,7 @@
         <v>45475</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19740,7 +19740,7 @@
         <v>45665</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19818,7 +19818,7 @@
         <v>44859</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>44999</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>45839</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45924</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>46267</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45555</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46294</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>46273</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45358</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20485,7 +20485,7 @@
         <v>46273</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20558,7 +20558,7 @@
         <v>46317</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20631,7 +20631,7 @@
         <v>46314</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>44888</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20777,7 +20777,7 @@
         <v>46317</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>46317</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
         <v>46317</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>46147</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>45357</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>45727</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>44966</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21288,7 +21288,7 @@
         <v>45034</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45617</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45359</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45020</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>44994</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>44851</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21731,7 +21731,7 @@
         <v>45357</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45357</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21877,7 +21877,7 @@
         <v>45468</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21950,7 +21950,7 @@
         <v>45645</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -22023,7 +22023,7 @@
         <v>45141</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45159</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22169,7 +22169,7 @@
         <v>45552</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>45379</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22315,7 +22315,7 @@
         <v>45184</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22388,7 +22388,7 @@
         <v>45076</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22461,7 +22461,7 @@
         <v>45028</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45182</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45653</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22680,7 +22680,7 @@
         <v>45691</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22753,7 +22753,7 @@
         <v>45033</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45772</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45769</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22972,7 +22972,7 @@
         <v>44606</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -23045,7 +23045,7 @@
         <v>45016</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45076</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>45028</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45086</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45236</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45089</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45183</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45110</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23629,7 +23629,7 @@
         <v>45007</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45384</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>44900</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45077</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45077</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>44959</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45379</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45122</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45159</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>44959</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>45304</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>45343</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45161</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45468</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45707</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>45552</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24807,7 +24807,7 @@
         <v>45593</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24880,7 +24880,7 @@
         <v>45126</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24953,7 +24953,7 @@
         <v>45600</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -25026,7 +25026,7 @@
         <v>45616</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25099,7 +25099,7 @@
         <v>45161</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25172,7 +25172,7 @@
         <v>44578</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25245,7 +25245,7 @@
         <v>45356</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45572</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45124</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25464,7 +25464,7 @@
         <v>45126</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>45000</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>45357</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45068</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25756,7 +25756,7 @@
         <v>45084</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25829,7 +25829,7 @@
         <v>45616</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25902,7 +25902,7 @@
         <v>45316</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25975,7 +25975,7 @@
         <v>45610</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26048,7 +26048,7 @@
         <v>45364</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>45372</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26194,7 +26194,7 @@
         <v>45372</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26267,7 +26267,7 @@
         <v>45665</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26345,7 +26345,7 @@
         <v>44705</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>45146</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>44678</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26564,7 +26564,7 @@
         <v>44623</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26637,7 +26637,7 @@
         <v>45404</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26710,7 +26710,7 @@
         <v>44700</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>44671</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26861,7 +26861,7 @@
         <v>44739</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>44721</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -27007,7 +27007,7 @@
         <v>45159</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27080,7 +27080,7 @@
         <v>45762</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27158,7 +27158,7 @@
         <v>45775</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>45300</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45769</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45304</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>45365</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27533,7 +27533,7 @@
         <v>45763</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27611,7 +27611,7 @@
         <v>44847</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27684,7 +27684,7 @@
         <v>45393</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>45365</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45365</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>45574</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>44524</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28059,7 +28059,7 @@
         <v>44565</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28132,7 +28132,7 @@
         <v>44985</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28205,7 +28205,7 @@
         <v>44952</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28278,7 +28278,7 @@
         <v>44603</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28351,7 +28351,7 @@
         <v>44848</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28424,7 +28424,7 @@
         <v>44886</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28497,7 +28497,7 @@
         <v>45063</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28570,7 +28570,7 @@
         <v>45546</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28643,7 +28643,7 @@
         <v>44886</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28716,7 +28716,7 @@
         <v>45069</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45135</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>44886</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         <v>44886</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -29008,7 +29008,7 @@
         <v>45702</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         <v>46029</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>46135</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
